--- a/BDP/BDP_INSIGHT_v0_1_1_PUBLIC_UPLOAD_BUNDLE_v1/BDP_L2_HodgeConverter_v0_1_1_Note/BDP_L2_HodgeConverter_v0_1_1_Workbook_EN.xlsx
+++ b/BDP/BDP_INSIGHT_v0_1_1_PUBLIC_UPLOAD_BUNDLE_v1/BDP_L2_HodgeConverter_v0_1_1_Note/BDP_L2_HodgeConverter_v0_1_1_Workbook_EN.xlsx
@@ -20,7 +20,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Claude_Handoff" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Experiment_Log'!$A$3:$H$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Experiment_Log'!$A$3:$N$32</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -29,7 +29,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -92,6 +92,10 @@
       <color rgb="00000000"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Liberation Sans"/>
+      <sz val="9"/>
+    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -141,7 +145,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -163,11 +167,55 @@
         <color rgb="00CFD6DC"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00CFD6DC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CFD6DC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CFD6DC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00CFD6DC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CFD6DC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CFD6DC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CFD6DC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CFD6DC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -242,6 +290,20 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -687,6 +749,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
@@ -694,6 +757,7 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10" ht="24" customHeight="1">
       <c r="A10" s="6" t="inlineStr">
         <is>
@@ -749,6 +813,7 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
     <row r="16" ht="24" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
@@ -836,6 +901,7 @@
         <v>29</v>
       </c>
     </row>
+    <row r="25"/>
     <row r="26" ht="24" customHeight="1">
       <c r="A26" s="6" t="inlineStr">
         <is>
@@ -854,6 +920,10 @@
           <t>5-minute first experiment, with recommended regex/wait/cont.</t>
         </is>
       </c>
+      <c r="C27" s="28" t="n"/>
+      <c r="D27" s="28" t="n"/>
+      <c r="E27" s="28" t="n"/>
+      <c r="F27" s="29" t="n"/>
     </row>
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="19" t="inlineStr">
@@ -866,6 +936,10 @@
           <t>All 29 experiments (Qwen 25 + Gemma 4); model output preserved verbatim.</t>
         </is>
       </c>
+      <c r="C28" s="28" t="n"/>
+      <c r="D28" s="28" t="n"/>
+      <c r="E28" s="28" t="n"/>
+      <c r="F28" s="29" t="n"/>
     </row>
     <row r="29" ht="22" customHeight="1">
       <c r="A29" s="19" t="inlineStr">
@@ -878,6 +952,10 @@
           <t>11 recommended public demonstration cases.</t>
         </is>
       </c>
+      <c r="C29" s="28" t="n"/>
+      <c r="D29" s="28" t="n"/>
+      <c r="E29" s="28" t="n"/>
+      <c r="F29" s="29" t="n"/>
     </row>
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="19" t="inlineStr">
@@ -890,6 +968,10 @@
           <t>Common failure / misunderstanding modes and mitigations.</t>
         </is>
       </c>
+      <c r="C30" s="28" t="n"/>
+      <c r="D30" s="28" t="n"/>
+      <c r="E30" s="28" t="n"/>
+      <c r="F30" s="29" t="n"/>
     </row>
     <row r="31" ht="22" customHeight="1">
       <c r="A31" s="19" t="inlineStr">
@@ -902,6 +984,10 @@
           <t>Goal-oriented regex / new_word / wait-cont presets.</t>
         </is>
       </c>
+      <c r="C31" s="28" t="n"/>
+      <c r="D31" s="28" t="n"/>
+      <c r="E31" s="28" t="n"/>
+      <c r="F31" s="29" t="n"/>
     </row>
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="19" t="inlineStr">
@@ -914,6 +1000,10 @@
           <t>Observed behavior — within-model 6.1–6.6 + cross-model 7.1–7.4.</t>
         </is>
       </c>
+      <c r="C32" s="28" t="n"/>
+      <c r="D32" s="28" t="n"/>
+      <c r="E32" s="28" t="n"/>
+      <c r="F32" s="29" t="n"/>
     </row>
     <row r="33" ht="22" customHeight="1">
       <c r="A33" s="19" t="inlineStr">
@@ -926,6 +1016,10 @@
           <t>Gemma4-4ae compatibility records + Token-Surface Conversion Hypothesis.</t>
         </is>
       </c>
+      <c r="C33" s="28" t="n"/>
+      <c r="D33" s="28" t="n"/>
+      <c r="E33" s="28" t="n"/>
+      <c r="F33" s="29" t="n"/>
     </row>
     <row r="34" ht="22" customHeight="1">
       <c r="A34" s="19" t="inlineStr">
@@ -938,6 +1032,10 @@
           <t>Free / Paid / Future tier boundary + privacy + customer-vs-provider credentials.</t>
         </is>
       </c>
+      <c r="C34" s="28" t="n"/>
+      <c r="D34" s="28" t="n"/>
+      <c r="E34" s="28" t="n"/>
+      <c r="F34" s="29" t="n"/>
     </row>
     <row r="35" ht="22" customHeight="1">
       <c r="A35" s="19" t="inlineStr">
@@ -950,6 +1048,10 @@
           <t>Key definitions (English).</t>
         </is>
       </c>
+      <c r="C35" s="28" t="n"/>
+      <c r="D35" s="28" t="n"/>
+      <c r="E35" s="28" t="n"/>
+      <c r="F35" s="29" t="n"/>
     </row>
     <row r="36" ht="22" customHeight="1">
       <c r="A36" s="19" t="inlineStr">
@@ -962,6 +1064,10 @@
           <t>Hand-off note for follow-up document work.</t>
         </is>
       </c>
+      <c r="C36" s="28" t="n"/>
+      <c r="D36" s="28" t="n"/>
+      <c r="E36" s="28" t="n"/>
+      <c r="F36" s="29" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="19">
@@ -1599,6 +1705,8 @@
           <t>If the model emits only the answer, the target never appears in the partial output. Use formula-guided wording.</t>
         </is>
       </c>
+      <c r="C13" s="28" t="n"/>
+      <c r="D13" s="29" t="n"/>
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="19" t="inlineStr">
@@ -1611,6 +1719,8 @@
           <t>A weak local model may fail arithmetic even without intervention. Apply the 5-stage decomposition.</t>
         </is>
       </c>
+      <c r="C14" s="28" t="n"/>
+      <c r="D14" s="29" t="n"/>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="19" t="inlineStr">
@@ -1623,6 +1733,8 @@
           <t>Some natural-language templates may reorder operands after the patch (see EXP-A02 / A03).</t>
         </is>
       </c>
+      <c r="C15" s="28" t="n"/>
+      <c r="D15" s="29" t="n"/>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="19" t="inlineStr">
@@ -1635,6 +1747,8 @@
           <t>If wait_tokens is too small, output may be cut mid-phrase, breaking meaning.</t>
         </is>
       </c>
+      <c r="C16" s="28" t="n"/>
+      <c r="D16" s="29" t="n"/>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="19" t="inlineStr">
@@ -1647,6 +1761,8 @@
           <t>Without a target-first breakpoint, the old answer may persist.</t>
         </is>
       </c>
+      <c r="C17" s="28" t="n"/>
+      <c r="D17" s="29" t="n"/>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="19" t="inlineStr">
@@ -1659,6 +1775,8 @@
           <t>new_word equal to an already-common token can cause unexpected re-orderings.</t>
         </is>
       </c>
+      <c r="C18" s="28" t="n"/>
+      <c r="D18" s="29" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -1681,17 +1799,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:N32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="38" customWidth="1" min="6" max="6"/>
-    <col width="38" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="28" customWidth="1" min="11" max="11"/>
+    <col width="26" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="36" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -1709,725 +1833,1277 @@
       </c>
       <c r="B3" s="21" t="inlineStr">
         <is>
+          <t>CategoryGroup</t>
+        </is>
+      </c>
+      <c r="C3" s="21" t="inlineStr">
+        <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="C3" s="21" t="inlineStr">
+      <c r="D3" s="21" t="inlineStr">
+        <is>
+          <t>Prompt</t>
+        </is>
+      </c>
+      <c r="E3" s="21" t="inlineStr">
+        <is>
+          <t>Before</t>
+        </is>
+      </c>
+      <c r="F3" s="21" t="inlineStr">
         <is>
           <t>Change</t>
         </is>
       </c>
-      <c r="D3" s="21" t="inlineStr">
+      <c r="G3" s="21" t="inlineStr">
+        <is>
+          <t>new_word</t>
+        </is>
+      </c>
+      <c r="H3" s="21" t="inlineStr">
         <is>
           <t>target_regex</t>
         </is>
       </c>
-      <c r="E3" s="21" t="inlineStr">
-        <is>
-          <t>wait/cont</t>
-        </is>
-      </c>
-      <c r="F3" s="21" t="inlineStr">
-        <is>
-          <t>Before</t>
-        </is>
-      </c>
-      <c r="G3" s="21" t="inlineStr">
+      <c r="I3" s="21" t="inlineStr">
+        <is>
+          <t>wait_tokens</t>
+        </is>
+      </c>
+      <c r="J3" s="21" t="inlineStr">
+        <is>
+          <t>continuation_tokens</t>
+        </is>
+      </c>
+      <c r="K3" s="21" t="inlineStr">
         <is>
           <t>After</t>
         </is>
       </c>
-      <c r="H3" s="21" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="23" t="inlineStr">
+      <c r="L3" s="21" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="M3" s="21" t="inlineStr">
+        <is>
+          <t>StatusGroup</t>
+        </is>
+      </c>
+      <c r="N3" s="21" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="30" t="inlineStr">
         <is>
           <t>EXP-A01</t>
         </is>
       </c>
-      <c r="B4" s="23" t="inlineStr">
+      <c r="B4" s="30" t="inlineStr">
         <is>
           <t>arithmetic</t>
         </is>
       </c>
-      <c r="C4" s="23" t="inlineStr">
-        <is>
-          <t>산술연산 / 왼쪽 피연산자 변경</t>
-        </is>
-      </c>
-      <c r="D4" s="23" t="inlineStr">
+      <c r="C4" s="30" t="inlineStr">
+        <is>
+          <t>arithmetic / left-operand swap</t>
+        </is>
+      </c>
+      <c r="D4" s="30" t="inlineStr">
         <is>
           <t>2 + 9 는?</t>
         </is>
       </c>
-      <c r="E4" s="23" t="inlineStr">
+      <c r="E4" s="30" t="inlineStr">
         <is>
           <t>2 + 9 = 11</t>
         </is>
       </c>
-      <c r="F4" s="23" t="inlineStr">
+      <c r="F4" s="30" t="inlineStr">
         <is>
           <t>2 -&gt; 9</t>
         </is>
       </c>
-      <c r="G4" s="23" t="inlineStr">
+      <c r="G4" s="30" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="H4" s="23" t="inlineStr">
+      <c r="H4" s="30" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="24" t="inlineStr">
+      <c r="I4" s="30" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" s="30" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K4" s="30" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="L4" s="30" t="inlineStr">
+        <is>
+          <t>Early breakpoint artifact</t>
+        </is>
+      </c>
+      <c r="M4" s="30" t="inlineStr">
+        <is>
+          <t>Breakpoint / tail artifact</t>
+        </is>
+      </c>
+      <c r="N4" s="30" t="inlineStr">
+        <is>
+          <t>wait_tokens 8, continuation_tokens 24
+9 -&gt; 4 변경시 성공
+[wait_tokens 8, continuation_tokens 24]</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="36" customHeight="1">
+      <c r="A5" s="31" t="inlineStr">
         <is>
           <t>EXP-A02</t>
         </is>
       </c>
-      <c r="B5" s="24" t="inlineStr">
+      <c r="B5" s="31" t="inlineStr">
         <is>
           <t>arithmetic</t>
         </is>
       </c>
-      <c r="C5" s="24" t="inlineStr">
-        <is>
-          <t>산술연산 / 왼쪽 피연산자 변경 / 영어 자연어 template 비교</t>
-        </is>
-      </c>
-      <c r="D5" s="24" t="inlineStr">
+      <c r="C5" s="31" t="inlineStr">
+        <is>
+          <t>arithmetic / left-operand swap / english natural-language template comparison</t>
+        </is>
+      </c>
+      <c r="D5" s="31" t="inlineStr">
         <is>
           <t>2 + 9 is?</t>
         </is>
       </c>
-      <c r="E5" s="24" t="inlineStr">
+      <c r="E5" s="31" t="inlineStr">
         <is>
           <t>The sum of 2 and 9 is 11.</t>
         </is>
       </c>
-      <c r="F5" s="24" t="inlineStr">
+      <c r="F5" s="31" t="inlineStr">
         <is>
           <t>2 -&gt; 9</t>
         </is>
       </c>
-      <c r="G5" s="24" t="inlineStr">
+      <c r="G5" s="31" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="H5" s="24" t="inlineStr">
+      <c r="H5" s="31" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="23" t="inlineStr">
+      <c r="I5" s="31" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J5" s="31" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K5" s="31" t="inlineStr">
+        <is>
+          <t>Clean formula-prefix success - type special(메모참)</t>
+        </is>
+      </c>
+      <c r="L5" s="31" t="n"/>
+      <c r="M5" s="31" t="inlineStr">
+        <is>
+          <t>Success / observed influence</t>
+        </is>
+      </c>
+      <c r="N5" s="31" t="inlineStr">
+        <is>
+          <t>wait_tokens 5 이상부터 반응, 정답은 11을 9로 바꾸는 경우  wait_tokens 100, continuation_tokens 32 응답이 다음과 같이 바뀜 {The sum of 2 and 9 is 9.} 
+이후 토큰 변경의 결정적 증거 및 가설 1 발생
+설정값 
+new_word 8, target_regex(optional) 2
+wait_tokens 13, continuation_tokens 32
+경우 응답이 바뀜 
+{The sum of 8 and 9 is 17.}
+가설 1, 현재 호지컨버터 기능 일부 제한으로 인해 이미 AI 가 내부에서 확정한 토큰 내부 값으로 new_word를 지정하면 모델이 변경된 값 = 기존토큰에 있는 값 일경우 확률 분포로 포섭함.
+즉 A + B = 에서 A 를  B로 바꿀 경우. 토큰 후보에 A 랑 토큰값은 같으나 토큰 id는 다른 A_1(A랑 값은 같고 토큰아이디만 다름) 확률분포로 퍼져있을 경우 가정시. B(A-&gt;B), B, A1 형태로 모델이 이어서 연산이 B(A-&gt;B)와 B를 동일 분포 취급후 기조누 A와 토큰값이 같은 A 로 변환.
+증거
+프롬프트[2 + 9 is?]
+기존응답[The sum of 2 and 9 is 11.]
+2 -&gt; 9 로 바꾸는 작업시 [wait_tokens 13, continuation_tokens 32]
+[The sum of 9 and 2 is 11.]
+A + B 형태에서 B(A-&gt;B) + A(A_1) = 형태로 서로 위치 바뀜
+new_word 5 로 바꿀경우 
+[The sum of 5 and 9 is 14.] 
+응답나옴, 즉 토큰 후보 분포를 모델이 연산하면서 같은거 끼리 묶으면서 식 순서변화가 일어난다 확인.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="36" customHeight="1">
+      <c r="A6" s="30" t="inlineStr">
         <is>
           <t>EXP-A03</t>
         </is>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="30" t="inlineStr">
         <is>
           <t>arithmetic</t>
         </is>
       </c>
-      <c r="C6" s="23" t="inlineStr">
-        <is>
-          <t>산술연산 / 수식 유도</t>
-        </is>
-      </c>
-      <c r="D6" s="23" t="inlineStr">
+      <c r="C6" s="30" t="inlineStr">
+        <is>
+          <t>arithmetic / 수식 유도</t>
+        </is>
+      </c>
+      <c r="D6" s="30" t="inlineStr">
         <is>
           <t>2 + 9 =</t>
         </is>
       </c>
-      <c r="E6" s="23" t="inlineStr">
+      <c r="E6" s="30" t="inlineStr">
         <is>
           <t>The answer to 2 + 9 is 11.</t>
         </is>
       </c>
-      <c r="F6" s="23" t="inlineStr">
+      <c r="F6" s="30" t="inlineStr">
         <is>
           <t>2 -&gt; 9</t>
         </is>
       </c>
-      <c r="G6" s="23" t="inlineStr">
+      <c r="G6" s="30" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="H6" s="23" t="inlineStr">
+      <c r="H6" s="30" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="24" t="inlineStr">
+      <c r="I6" s="30" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J6" s="30" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K6" s="30" t="inlineStr">
+        <is>
+          <t>The answer to 2 + 9 is 11.</t>
+        </is>
+      </c>
+      <c r="L6" s="30" t="inlineStr">
+        <is>
+          <t>No target detected</t>
+        </is>
+      </c>
+      <c r="M6" s="30" t="inlineStr">
+        <is>
+          <t>No target / inactive</t>
+        </is>
+      </c>
+      <c r="N6" s="30" t="inlineStr">
+        <is>
+          <t>wait_tokens 13, continuation_tokens 32 으로 셋팅시 작동 
+EXP-A02 와 같이 [The answer to 9 + 2 is 11.] 응답시 순서 바뀜 발생
+new_word 2 -&gt; 8 로 변경시 [The answer to 8 is 10.]
+new_word 2 -&gt; 3 로 변경시[The answer to 3 is 11.]
+wait_tokens 8, continuation_tokens 24
+new_word 2 -&gt; 4 [The sum of 4 and 9 is 13.]
+new_word 9 -&gt; 4 [The sum of 2 and 4 is 6.]
+[Clean formula-prefix success] 발생</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="36" customHeight="1">
+      <c r="A7" s="31" t="inlineStr">
         <is>
           <t>EXP-A04</t>
         </is>
       </c>
-      <c r="B7" s="24" t="inlineStr">
+      <c r="B7" s="31" t="inlineStr">
         <is>
           <t>arithmetic</t>
         </is>
       </c>
-      <c r="C7" s="24" t="inlineStr">
-        <is>
-          <t>산술연산 / 수식 유도 / 좁은 regex</t>
-        </is>
-      </c>
-      <c r="D7" s="24" t="inlineStr">
+      <c r="C7" s="31" t="inlineStr">
+        <is>
+          <t>arithmetic / 수식 유도 / 좁은 regex</t>
+        </is>
+      </c>
+      <c r="D7" s="31" t="inlineStr">
         <is>
           <t>2 + 9 =</t>
         </is>
       </c>
-      <c r="E7" s="24" t="inlineStr">
+      <c r="E7" s="31" t="inlineStr">
         <is>
           <t>The answer to 2 + 9 is 11.</t>
         </is>
       </c>
-      <c r="F7" s="24" t="inlineStr">
+      <c r="F7" s="31" t="inlineStr">
         <is>
           <t>2 -&gt; 4</t>
         </is>
       </c>
-      <c r="G7" s="24" t="inlineStr">
+      <c r="G7" s="31" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="H7" s="24" t="inlineStr">
+      <c r="H7" s="31" t="inlineStr">
         <is>
           <t>(?&lt;!\d)2(?=\s*\+)</t>
         </is>
       </c>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="23" t="inlineStr">
+      <c r="I7" s="31" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J7" s="31" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K7" s="31" t="inlineStr">
+        <is>
+          <t>변경토큰{target_regex [2?, 2*]} -&gt; [4The answer is 4.] 
+변경토큰{target_regex [2+]} -&gt; The answer to 4 is 11.</t>
+        </is>
+      </c>
+      <c r="L7" s="31" t="inlineStr">
+        <is>
+          <t>Formula-guided continuation succes</t>
+        </is>
+      </c>
+      <c r="M7" s="31" t="inlineStr">
+        <is>
+          <t>Success / observed influence</t>
+        </is>
+      </c>
+      <c r="N7" s="31" t="inlineStr">
+        <is>
+          <t>뒤의 연산자가 토큰이 값을 판단하는 형태인 ~? 혹은 강조 표시로 2* 쓰는 경우 반응한 것으로 예측. 2+ 경우 연산자가 2 + 형태라 반응한 것이라 추측 했으나.
+기존 [ 2 - 9 =] -&gt; 기존 결과 [The result of 2 minus 9 is -7.]
+[wait_tokens 8, continuation_tokens 24] [2+ -&gt;4 로변경]
+결과 [The result of 4 is: -5] 로 나옴. 즉 2+ 가 양수 음수 나타내는 형태로도 붙는지도 확인 필요. 예시 2-&gt; 판단 위해 [2?] 강조를 위해 [2*] 정수표시 [2+].
+확인을 위해 [-2 - 9] 실험
+기존 [The result of subtracting 9 from -2 is -11.]
+변경[2+ -&gt; 4] 결과 [The result of subtracting 9 from -2 is -11.]
+추가로 [wait_tokens 13, continuation_tokens 32] + [2 -&gt;4]변경시 
+[The result of subtracting 9 from -4 is -13.]
+또한 [-2 -&gt; 4] 경우 wait_tokens과 continuation_tokens를 바꿔봐도 호지컨버터 반응없음
+하지만 [\-2 -&gt; 4 경우 ][wait_tokens 13, continuation_tokens 32]
+결과 [he result of subtracting 9 from 4 is -5.] 변경 
+추가 확인결과 [-2 -&gt; \-2, \-2* , \-2?, \-2+] 로 변경시 제대로 반응
+[\-2+] 역시 반응하는거로 봐서는 문제가 [ -2 - 9 = ]라 해도 내부적으론 -2(+) 앞은 음수 숫자 내부는 정수 취급으로 추측가능.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="36" customHeight="1">
+      <c r="A8" s="31" t="inlineStr">
         <is>
           <t>EXP-A05</t>
         </is>
       </c>
-      <c r="B8" s="23" t="inlineStr">
+      <c r="B8" s="31" t="inlineStr">
         <is>
           <t>arithmetic</t>
         </is>
       </c>
-      <c r="C8" s="23" t="inlineStr">
-        <is>
-          <t>산술연산 / 오른쪽 피연산자 변경</t>
-        </is>
-      </c>
-      <c r="D8" s="23" t="inlineStr">
+      <c r="C8" s="31" t="inlineStr">
+        <is>
+          <t>arithmetic / right-operand swap</t>
+        </is>
+      </c>
+      <c r="D8" s="31" t="inlineStr">
         <is>
           <t>2 + 4 는?</t>
         </is>
       </c>
-      <c r="E8" s="23" t="inlineStr">
+      <c r="E8" s="31" t="inlineStr">
         <is>
           <t>2 + 4 = 6</t>
         </is>
       </c>
-      <c r="F8" s="23" t="inlineStr">
+      <c r="F8" s="31" t="inlineStr">
         <is>
           <t>4 -&gt; 9</t>
         </is>
       </c>
-      <c r="G8" s="23" t="inlineStr">
+      <c r="G8" s="31" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="H8" s="23" t="inlineStr">
+      <c r="H8" s="31" t="inlineStr">
         <is>
           <t>(?&lt;=\+)\s*\d+</t>
         </is>
       </c>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="24" t="inlineStr">
+      <c r="I8" s="31" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J8" s="31" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K8" s="31" t="inlineStr">
+        <is>
+          <t>2 + 9 = 11</t>
+        </is>
+      </c>
+      <c r="L8" s="31" t="inlineStr">
+        <is>
+          <t>Clean formula-prefix success</t>
+        </is>
+      </c>
+      <c r="M8" s="31" t="inlineStr">
+        <is>
+          <t>Success / observed influence</t>
+        </is>
+      </c>
+      <c r="N8" s="31" t="n"/>
+    </row>
+    <row r="9" ht="36" customHeight="1">
+      <c r="A9" s="31" t="inlineStr">
         <is>
           <t>EXP-A06</t>
         </is>
       </c>
-      <c r="B9" s="24" t="inlineStr">
+      <c r="B9" s="31" t="inlineStr">
         <is>
           <t>arithmetic</t>
         </is>
       </c>
-      <c r="C9" s="24" t="inlineStr">
-        <is>
-          <t>산술연산 / 결과값 변경</t>
-        </is>
-      </c>
-      <c r="D9" s="24" t="inlineStr">
+      <c r="C9" s="31" t="inlineStr">
+        <is>
+          <t>arithmetic / 결과값 변경</t>
+        </is>
+      </c>
+      <c r="D9" s="31" t="inlineStr">
         <is>
           <t>2 + 4 는?</t>
         </is>
       </c>
-      <c r="E9" s="24" t="inlineStr">
+      <c r="E9" s="31" t="inlineStr">
         <is>
           <t>2 + 4 = 6</t>
         </is>
       </c>
-      <c r="F9" s="24" t="inlineStr">
+      <c r="F9" s="31" t="inlineStr">
         <is>
           <t>결과값 -&gt; 99</t>
         </is>
       </c>
-      <c r="G9" s="24" t="inlineStr">
+      <c r="G9" s="31" t="inlineStr">
         <is>
           <t>99</t>
         </is>
       </c>
-      <c r="H9" s="24" t="inlineStr">
+      <c r="H9" s="31" t="inlineStr">
         <is>
           <t>(?&lt;==\s*)\d+</t>
         </is>
       </c>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="23" t="inlineStr">
+      <c r="I9" s="31" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J9" s="31" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K9" s="31" t="inlineStr">
+        <is>
+          <t>2 + 4 = 99</t>
+        </is>
+      </c>
+      <c r="L9" s="31" t="inlineStr">
+        <is>
+          <t>Clean formula-prefix success</t>
+        </is>
+      </c>
+      <c r="M9" s="31" t="inlineStr">
+        <is>
+          <t>Success / observed influence</t>
+        </is>
+      </c>
+      <c r="N9" s="31" t="inlineStr">
+        <is>
+          <t>[6? -&gt; 99] 결과 [ 992](공백이 실제로 나옴)
+[= 6 -&gt; 99 ] [2 + 4 99]
+실제 답을 만든 끝단만 변화 시킨느낌이 들어서 추가 확
+[2 + 4 는? 계산 이후 값 검산, 고치기 금지]
+기존 [2 + 4은 6입니다.]
+[6 -&gt; 99] 변경결과 [2 + 4은 99.00000000000001 이 됩니다.]
+검산시 실제 변경에 따른 반응 추가됨
+결과를 다시 사용할 경우 영향 실제로 받음</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="36" customHeight="1">
+      <c r="A10" s="31" t="inlineStr">
         <is>
           <t>EXP-A07</t>
         </is>
       </c>
-      <c r="B10" s="23" t="inlineStr">
+      <c r="B10" s="31" t="inlineStr">
         <is>
           <t>arithmetic</t>
         </is>
       </c>
-      <c r="C10" s="23" t="inlineStr">
-        <is>
-          <t>산술연산 / 연산자 변경 plus -&gt; minus</t>
-        </is>
-      </c>
-      <c r="D10" s="23" t="inlineStr">
+      <c r="C10" s="31" t="inlineStr">
+        <is>
+          <t>arithmetic / operator swap plus -&gt; minus</t>
+        </is>
+      </c>
+      <c r="D10" s="31" t="inlineStr">
         <is>
           <t>2 + 4 는?</t>
         </is>
       </c>
-      <c r="E10" s="23" t="inlineStr">
+      <c r="E10" s="31" t="inlineStr">
         <is>
           <t>2 + 4 = 6</t>
         </is>
       </c>
-      <c r="F10" s="23" t="inlineStr">
+      <c r="F10" s="31" t="inlineStr">
         <is>
           <t>+ -&gt; -</t>
         </is>
       </c>
-      <c r="G10" s="23" t="inlineStr">
+      <c r="G10" s="31" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H10" s="23" t="inlineStr">
+      <c r="H10" s="31" t="inlineStr">
         <is>
           <t>\+</t>
         </is>
       </c>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="24" t="inlineStr">
+      <c r="I10" s="31" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J10" s="31" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K10" s="31" t="inlineStr">
+        <is>
+          <t>2 - 4 = -2</t>
+        </is>
+      </c>
+      <c r="L10" s="31" t="inlineStr">
+        <is>
+          <t>Clean formula-prefix success</t>
+        </is>
+      </c>
+      <c r="M10" s="31" t="inlineStr">
+        <is>
+          <t>Success / observed influence</t>
+        </is>
+      </c>
+      <c r="N10" s="31" t="n"/>
+    </row>
+    <row r="11" ht="36" customHeight="1">
+      <c r="A11" s="31" t="inlineStr">
         <is>
           <t>EXP-A08</t>
         </is>
       </c>
-      <c r="B11" s="24" t="inlineStr">
+      <c r="B11" s="31" t="inlineStr">
         <is>
           <t>arithmetic</t>
         </is>
       </c>
-      <c r="C11" s="24" t="inlineStr">
-        <is>
-          <t>산술연산 / 연산자 변경 plus -&gt; multiply</t>
-        </is>
-      </c>
-      <c r="D11" s="24" t="inlineStr">
+      <c r="C11" s="31" t="inlineStr">
+        <is>
+          <t>arithmetic / operator swap plus -&gt; multiply</t>
+        </is>
+      </c>
+      <c r="D11" s="31" t="inlineStr">
         <is>
           <t>2 + 4 는?</t>
         </is>
       </c>
-      <c r="E11" s="24" t="inlineStr"/>
-      <c r="F11" s="24" t="inlineStr">
+      <c r="E11" s="31" t="n"/>
+      <c r="F11" s="31" t="inlineStr">
         <is>
           <t>+ -&gt; *</t>
         </is>
       </c>
-      <c r="G11" s="24" t="inlineStr">
+      <c r="G11" s="31" t="inlineStr">
         <is>
           <t>*</t>
         </is>
       </c>
-      <c r="H11" s="24" t="inlineStr">
+      <c r="H11" s="31" t="inlineStr">
         <is>
           <t>\+</t>
         </is>
       </c>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="23" t="inlineStr">
+      <c r="I11" s="31" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J11" s="31" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K11" s="31" t="inlineStr">
+        <is>
+          <t>Clean formula-prefix success</t>
+        </is>
+      </c>
+      <c r="L11" s="31" t="inlineStr">
+        <is>
+          <t>2 * 4 = 8</t>
+        </is>
+      </c>
+      <c r="M11" s="31" t="inlineStr">
+        <is>
+          <t>Success / observed influence</t>
+        </is>
+      </c>
+      <c r="N11" s="31" t="n"/>
+    </row>
+    <row r="12" ht="36" customHeight="1">
+      <c r="A12" s="31" t="inlineStr">
         <is>
           <t>EXP-A09</t>
         </is>
       </c>
-      <c r="B12" s="23" t="inlineStr">
+      <c r="B12" s="31" t="inlineStr">
         <is>
           <t>arithmetic</t>
         </is>
       </c>
-      <c r="C12" s="23" t="inlineStr">
-        <is>
-          <t>산술연산 / formula-guided 성공 후보</t>
-        </is>
-      </c>
-      <c r="D12" s="23" t="inlineStr">
+      <c r="C12" s="31" t="inlineStr">
+        <is>
+          <t>arithmetic / formula-guided 성공 후보</t>
+        </is>
+      </c>
+      <c r="D12" s="31" t="inlineStr">
         <is>
           <t>2 + 7 한 값에 9를 더하면? 수식부터 쓰고 계산</t>
         </is>
       </c>
-      <c r="E12" s="23" t="inlineStr">
+      <c r="E12" s="31" t="inlineStr">
         <is>
           <t>2 + 7 + 9 = 18</t>
         </is>
       </c>
-      <c r="F12" s="23" t="inlineStr">
+      <c r="F12" s="31" t="inlineStr">
         <is>
           <t>9 -&gt; 14</t>
         </is>
       </c>
-      <c r="G12" s="23" t="inlineStr">
+      <c r="G12" s="31" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="H12" s="23" t="inlineStr">
+      <c r="H12" s="31" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="24" t="inlineStr">
+      <c r="I12" s="31" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J12" s="31" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="K12" s="31" t="inlineStr">
+        <is>
+          <t>2 + 7 + 14 = 23</t>
+        </is>
+      </c>
+      <c r="L12" s="31" t="inlineStr">
+        <is>
+          <t>Clean formula-prefix success</t>
+        </is>
+      </c>
+      <c r="M12" s="31" t="inlineStr">
+        <is>
+          <t>Success / observed influence</t>
+        </is>
+      </c>
+      <c r="N12" s="31" t="n"/>
+    </row>
+    <row r="13" ht="36" customHeight="1">
+      <c r="A13" s="31" t="inlineStr">
         <is>
           <t>EXP-A10</t>
         </is>
       </c>
-      <c r="B13" s="24" t="inlineStr">
+      <c r="B13" s="31" t="inlineStr">
         <is>
           <t>arithmetic</t>
         </is>
       </c>
-      <c r="C13" s="24" t="inlineStr">
-        <is>
-          <t>산술연산 / base model 한계 확인</t>
-        </is>
-      </c>
-      <c r="D13" s="24" t="inlineStr">
+      <c r="C13" s="31" t="inlineStr">
+        <is>
+          <t>arithmetic / base model 한계 확인</t>
+        </is>
+      </c>
+      <c r="D13" s="31" t="inlineStr">
         <is>
           <t>2 + 7 한 값에 9를 더하면?</t>
         </is>
       </c>
-      <c r="E13" s="24" t="inlineStr">
+      <c r="E13" s="31" t="inlineStr">
         <is>
           <t>2 + 7 + 9 = 18</t>
         </is>
       </c>
-      <c r="F13" s="24" t="inlineStr">
+      <c r="F13" s="31" t="inlineStr">
         <is>
           <t>없음</t>
         </is>
       </c>
-      <c r="G13" s="24" t="inlineStr"/>
-      <c r="H13" s="24" t="inlineStr">
+      <c r="G13" s="31" t="n"/>
+      <c r="H13" s="31" t="inlineStr">
         <is>
           <t>없음</t>
         </is>
       </c>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="23" t="inlineStr">
+      <c r="I13" s="31" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="J13" s="31" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="K13" s="31" t="inlineStr">
+        <is>
+          <t>2 + 7 + 9 = 18</t>
+        </is>
+      </c>
+      <c r="L13" s="31" t="inlineStr">
+        <is>
+          <t>Clean formula-prefix success</t>
+        </is>
+      </c>
+      <c r="M13" s="31" t="inlineStr">
+        <is>
+          <t>Success / observed influence</t>
+        </is>
+      </c>
+      <c r="N13" s="31" t="inlineStr">
+        <is>
+          <t>base가 원래 틀리는지 확인용</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="36" customHeight="1">
+      <c r="A14" s="32" t="inlineStr">
         <is>
           <t>EXP-A11</t>
         </is>
       </c>
-      <c r="B14" s="23" t="inlineStr">
+      <c r="B14" s="32" t="inlineStr">
         <is>
           <t>arithmetic</t>
         </is>
       </c>
-      <c r="C14" s="23" t="inlineStr">
-        <is>
-          <t>산술연산 / base model 한계 확인 / 숫자만</t>
-        </is>
-      </c>
-      <c r="D14" s="23" t="inlineStr">
+      <c r="C14" s="32" t="inlineStr">
+        <is>
+          <t>arithmetic / base model 한계 확인 / 숫자만</t>
+        </is>
+      </c>
+      <c r="D14" s="32" t="inlineStr">
         <is>
           <t>2 + 7 한 값에 9를 더하면? 숫자만</t>
         </is>
       </c>
-      <c r="E14" s="23" t="inlineStr">
+      <c r="E14" s="32" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="F14" s="23" t="inlineStr">
+      <c r="F14" s="32" t="inlineStr">
         <is>
           <t>없음</t>
         </is>
       </c>
-      <c r="G14" s="23" t="inlineStr"/>
-      <c r="H14" s="23" t="inlineStr">
+      <c r="G14" s="32" t="n"/>
+      <c r="H14" s="32" t="inlineStr">
         <is>
           <t>없음</t>
         </is>
       </c>
-    </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="24" t="inlineStr">
+      <c r="I14" s="32" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="J14" s="32" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="K14" s="32" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L14" s="32" t="inlineStr">
+        <is>
+          <t>Base model arithmetic failure]</t>
+        </is>
+      </c>
+      <c r="M14" s="32" t="inlineStr">
+        <is>
+          <t>Base / model limitation</t>
+        </is>
+      </c>
+      <c r="N14" s="32" t="inlineStr">
+        <is>
+          <t>base가 원래 틀리는지 확인용
+========================
+B. 중간값 변경 / 후속 계산 영향
+========================</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="36" customHeight="1">
+      <c r="A15" s="30" t="inlineStr">
         <is>
           <t>EXP-B01</t>
         </is>
       </c>
-      <c r="B15" s="24" t="inlineStr">
-        <is>
-          <t>중간값 변경</t>
-        </is>
-      </c>
-      <c r="C15" s="24" t="inlineStr">
-        <is>
-          <t>중간값 변경 / 후속 계산 반영</t>
-        </is>
-      </c>
-      <c r="D15" s="24" t="inlineStr">
+      <c r="B15" s="30" t="inlineStr">
+        <is>
+          <t>mid-value substitution</t>
+        </is>
+      </c>
+      <c r="C15" s="30" t="inlineStr">
+        <is>
+          <t>mid-value substitution / 후속 계산 반영</t>
+        </is>
+      </c>
+      <c r="D15" s="30" t="inlineStr">
         <is>
           <t>1 + 1 을 한 이후에 3 을 더하면?</t>
         </is>
       </c>
-      <c r="E15" s="24" t="inlineStr">
+      <c r="E15" s="30" t="inlineStr">
         <is>
           <t>1 + 1 = 2
 그 후에 3을 더하면 5입니다.</t>
         </is>
       </c>
-      <c r="F15" s="24" t="inlineStr">
+      <c r="F15" s="30" t="inlineStr">
         <is>
           <t>2 -&gt; 9</t>
         </is>
       </c>
-      <c r="G15" s="24" t="inlineStr">
+      <c r="G15" s="30" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="H15" s="24" t="inlineStr">
+      <c r="H15" s="30" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-    </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="23" t="inlineStr">
+      <c r="I15" s="30" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J15" s="30" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K15" s="30" t="inlineStr">
+        <is>
+          <t>1 + 1 = 9</t>
+        </is>
+      </c>
+      <c r="L15" s="30" t="n"/>
+      <c r="M15" s="30" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
+      <c r="N15" s="30" t="inlineStr">
+        <is>
+          <t>기대 관찰 예시 = 1+1=9, 이후 3 더해서 12</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="36" customHeight="1">
+      <c r="A16" s="31" t="inlineStr">
         <is>
           <t>EXP-B02</t>
         </is>
       </c>
-      <c r="B16" s="23" t="inlineStr">
-        <is>
-          <t>중간값 변경</t>
-        </is>
-      </c>
-      <c r="C16" s="23" t="inlineStr">
-        <is>
-          <t>중간값 변경 / 수식부터 쓰기</t>
-        </is>
-      </c>
-      <c r="D16" s="23" t="inlineStr">
+      <c r="B16" s="31" t="inlineStr">
+        <is>
+          <t>mid-value substitution</t>
+        </is>
+      </c>
+      <c r="C16" s="31" t="inlineStr">
+        <is>
+          <t>mid-value substitution / 수식부터 쓰기</t>
+        </is>
+      </c>
+      <c r="D16" s="31" t="inlineStr">
         <is>
           <t>1 + 1 을 계산하고, 그 결과에 3을 더하는 수식을 먼저 쓰고 계산해</t>
         </is>
       </c>
-      <c r="E16" s="23" t="inlineStr">
+      <c r="E16" s="31" t="inlineStr">
         <is>
           <t>1 + 1 = 2
 2 + 3 = 5</t>
         </is>
       </c>
-      <c r="F16" s="23" t="inlineStr">
+      <c r="F16" s="31" t="inlineStr">
         <is>
           <t>2 -&gt; 9</t>
         </is>
       </c>
-      <c r="G16" s="23" t="inlineStr">
+      <c r="G16" s="31" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="H16" s="23" t="inlineStr">
+      <c r="H16" s="31" t="inlineStr">
         <is>
           <t>(?&lt;==\s*)\d+</t>
         </is>
       </c>
-    </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="24" t="inlineStr">
+      <c r="I16" s="31" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="J16" s="31" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K16" s="31" t="inlineStr">
+        <is>
+          <t>1 + 1 = 9
+계산 후, 9를 3으로 더하면 12입니다.</t>
+        </is>
+      </c>
+      <c r="L16" s="31" t="inlineStr">
+        <is>
+          <t>Clean formula-prefix success</t>
+        </is>
+      </c>
+      <c r="M16" s="31" t="inlineStr">
+        <is>
+          <t>Success / observed influence</t>
+        </is>
+      </c>
+      <c r="N16" s="31" t="inlineStr">
+        <is>
+          <t>결과값 위치를 잡는 실험
+번외: [
+{you&gt; 1 + 1 을 계산하고, 그 결과에 3을 더하는 수식을 먼저 쓰고 계산해. 이후 검산
+m13&gt;  계산: 1 + 1 = 2
+결과: 2
+계산 후, 2를 3으로 더하면:
+2
+} 2 -&gt; 9 로 변경시
+{계산: 1 + 1 = 9
+계산 후, 9를 3으로 나누면 3가 됩니다.
+결과: 3}
+이전에는 계산 오류 라면 여기선 가중치 높은 토큰 쪽으로 환각 작용 발생 예측가능
+ ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="36" customHeight="1">
+      <c r="A17" s="30" t="inlineStr">
         <is>
           <t>EXP-B03</t>
         </is>
       </c>
-      <c r="B17" s="24" t="inlineStr">
-        <is>
-          <t>중간값 변경</t>
-        </is>
-      </c>
-      <c r="C17" s="24" t="inlineStr">
-        <is>
-          <t>중간값 변경 / 오른쪽 항목 영향</t>
-        </is>
-      </c>
-      <c r="D17" s="24" t="inlineStr">
+      <c r="B17" s="30" t="inlineStr">
+        <is>
+          <t>mid-value substitution</t>
+        </is>
+      </c>
+      <c r="C17" s="30" t="inlineStr">
+        <is>
+          <t>mid-value substitution / 오른쪽 항목 영향</t>
+        </is>
+      </c>
+      <c r="D17" s="30" t="inlineStr">
         <is>
           <t>5 + 2 를 계산한 뒤, 그 값에 4를 더해</t>
         </is>
       </c>
-      <c r="E17" s="24" t="inlineStr">
+      <c r="E17" s="30" t="inlineStr">
         <is>
           <t>계산 결과는 7입니다.</t>
         </is>
       </c>
-      <c r="F17" s="24" t="inlineStr">
+      <c r="F17" s="30" t="inlineStr">
         <is>
           <t>2 -&gt; 9</t>
         </is>
       </c>
-      <c r="G17" s="24" t="inlineStr">
+      <c r="G17" s="30" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="H17" s="24" t="inlineStr">
+      <c r="H17" s="30" t="inlineStr">
         <is>
           <t>(?&lt;=\+)\s*2</t>
         </is>
       </c>
-    </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="23" t="inlineStr">
+      <c r="I17" s="30" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="J17" s="30" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K17" s="30" t="inlineStr">
+        <is>
+          <t>호지 컨버터 작동안</t>
+        </is>
+      </c>
+      <c r="L17" s="30" t="inlineStr">
+        <is>
+          <t>Base model arithmetic failure, No target detected</t>
+        </is>
+      </c>
+      <c r="M17" s="30" t="inlineStr">
+        <is>
+          <t>No target / inactive</t>
+        </is>
+      </c>
+      <c r="N17" s="30" t="inlineStr">
+        <is>
+          <t>5+2가 5+9로 바뀌는지 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="36" customHeight="1">
+      <c r="A18" s="31" t="inlineStr">
         <is>
           <t>EXP-B04</t>
         </is>
       </c>
-      <c r="B18" s="23" t="inlineStr">
-        <is>
-          <t>중간값 변경</t>
-        </is>
-      </c>
-      <c r="C18" s="23" t="inlineStr">
-        <is>
-          <t>중간값 변경 / 결과값만 변경</t>
-        </is>
-      </c>
-      <c r="D18" s="23" t="inlineStr">
+      <c r="B18" s="31" t="inlineStr">
+        <is>
+          <t>mid-value substitution</t>
+        </is>
+      </c>
+      <c r="C18" s="31" t="inlineStr">
+        <is>
+          <t>mid-value substitution / 결과값만 변경</t>
+        </is>
+      </c>
+      <c r="D18" s="31" t="inlineStr">
         <is>
           <t>5 + 2 를 계산한 뒤, 그 값에 4를 더해</t>
         </is>
       </c>
-      <c r="E18" s="23" t="inlineStr">
+      <c r="E18" s="31" t="inlineStr">
         <is>
           <t>계산 결과는 7입니다.</t>
         </is>
       </c>
-      <c r="F18" s="23" t="inlineStr">
+      <c r="F18" s="31" t="inlineStr">
         <is>
           <t>첫 계산 결과 -&gt; 20</t>
         </is>
       </c>
-      <c r="G18" s="23" t="inlineStr">
+      <c r="G18" s="31" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="H18" s="23" t="inlineStr">
+      <c r="H18" s="31" t="inlineStr">
         <is>
           <t>(?&lt;==\s*)\d+</t>
         </is>
       </c>
-    </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="24" t="inlineStr">
+      <c r="I18" s="31" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="J18" s="31" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K18" s="31" t="inlineStr">
+        <is>
+          <t>계산 결과는 9입니다.</t>
+        </is>
+      </c>
+      <c r="L18" s="31" t="inlineStr">
+        <is>
+          <t>Clean formula-prefix success</t>
+        </is>
+      </c>
+      <c r="M18" s="31" t="inlineStr">
+        <is>
+          <t>Success / observed influence</t>
+        </is>
+      </c>
+      <c r="N18" s="31" t="inlineStr">
+        <is>
+          <t>첫 결과값 수술 후 후속 continuation 영향 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="36" customHeight="1">
+      <c r="A19" s="32" t="inlineStr">
         <is>
           <t>EXP-B03-R1</t>
         </is>
       </c>
-      <c r="B19" s="24" t="inlineStr">
-        <is>
-          <t>중간값 변경</t>
-        </is>
-      </c>
-      <c r="C19" s="24" t="inlineStr">
-        <is>
-          <t>중간값 변경 / 오른쪽 항목 영향 / 수식 노출 유도</t>
-        </is>
-      </c>
-      <c r="D19" s="24" t="inlineStr">
+      <c r="B19" s="32" t="inlineStr">
+        <is>
+          <t>mid-value substitution</t>
+        </is>
+      </c>
+      <c r="C19" s="32" t="inlineStr">
+        <is>
+          <t>mid-value substitution / 오른쪽 항목 영향 / formula-guided</t>
+        </is>
+      </c>
+      <c r="D19" s="32" t="inlineStr">
         <is>
           <t>5 + 2 를 계산한 뒤, 그 값에 4를 더해. 먼저 반드시 "5 + 2 =" 형태의 수식을 한 줄로 쓰고, 그다음 이어서 계산해.</t>
         </is>
       </c>
-      <c r="E19" s="24" t="inlineStr">
+      <c r="E19" s="32" t="inlineStr">
         <is>
           <t>5 + 2 = 7
 7 + 4 = 11</t>
         </is>
       </c>
-      <c r="F19" s="24" t="inlineStr">
+      <c r="F19" s="32" t="inlineStr">
         <is>
           <t>2 -&gt; 9</t>
         </is>
       </c>
-      <c r="G19" s="24" t="inlineStr">
+      <c r="G19" s="32" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="H19" s="24" t="inlineStr">
+      <c r="H19" s="32" t="inlineStr">
         <is>
           <t>(?&lt;=\+)\s*2</t>
         </is>
       </c>
-    </row>
-    <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="23" t="inlineStr">
+      <c r="I19" s="32" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="J19" s="32" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K19" s="32" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="L19" s="32" t="inlineStr">
+        <is>
+          <t>Base model arithmetic failure + 현재 기능여러가지 빠진 호지컨버터 정밀도 이슈</t>
+        </is>
+      </c>
+      <c r="M19" s="32" t="inlineStr">
+        <is>
+          <t>Base / model limitation</t>
+        </is>
+      </c>
+      <c r="N19" s="32" t="inlineStr">
+        <is>
+          <t>partial output에 5 + 2가 실제로 나오는지 확인
+========================
+C. 문장형 수학 / 사과 예제
+========================</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="36" customHeight="1">
+      <c r="A20" s="31" t="inlineStr">
         <is>
           <t>EXP-C01</t>
         </is>
       </c>
-      <c r="B20" s="23" t="inlineStr">
-        <is>
-          <t>문장형 수학</t>
-        </is>
-      </c>
-      <c r="C20" s="23" t="inlineStr">
-        <is>
-          <t>문장형 수학 / 연산자 변경</t>
-        </is>
-      </c>
-      <c r="D20" s="23" t="inlineStr">
+      <c r="B20" s="31" t="inlineStr">
+        <is>
+          <t>word-problem math</t>
+        </is>
+      </c>
+      <c r="C20" s="31" t="inlineStr">
+        <is>
+          <t>word-problem math / operator swap</t>
+        </is>
+      </c>
+      <c r="D20" s="31" t="inlineStr">
         <is>
           <t>사과 2개를 가지고 있다가 4개를 더 받는 것을 수학 공식화하면? 수학 기호로 표현 후, 해당 기호 계산</t>
         </is>
       </c>
-      <c r="E20" s="23" t="inlineStr">
+      <c r="E20" s="31" t="inlineStr">
         <is>
           <t>사과 2개를 가지고 있다면, 이는 "2x" 또는 "2 + x" 형태의 수학 기호를 사용할 수 있습니다.
 수학 공식화 시, 이 기호를 "2 + 4"라고 표현하면 됩니다.
@@ -2436,44 +3112,81 @@
 따라서, 사과 2개를 받은 후에 4개 더 받으면, 그 결과는 6입니다.</t>
         </is>
       </c>
-      <c r="F20" s="23" t="inlineStr">
+      <c r="F20" s="31" t="inlineStr">
         <is>
           <t>+ -&gt; -</t>
         </is>
       </c>
-      <c r="G20" s="23" t="inlineStr">
+      <c r="G20" s="31" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H20" s="23" t="inlineStr">
+      <c r="H20" s="31" t="inlineStr">
         <is>
           <t>\+</t>
         </is>
       </c>
-    </row>
-    <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="24" t="inlineStr">
+      <c r="I20" s="31" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J20" s="31" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K20" s="31" t="inlineStr">
+        <is>
+          <t>사과 2개를 가지고 있다면, 이는 "2x" 또는 "2 - x" 형태의 수학 기호를 사용할 수 있습니다.
+수학 공식화 시, 이 기호를 "2 + 4"
+살짝 실험[사과 2개를 가지고 있다가 4개를 더 받는 것을 수학 공식화하면? 수학 기호로 표현 후, 해당 기호 계산, 고치기 금지 계속 계산]
+결과[사과 2개를 가지고 있다면, 4개를 더해보면 6개의 사과가 나온다.
+수학 기호로 표현하면:
+\( 2 - 1 + 3 = 6 \)
+이 계산은 기본적인 수학 기호와 연산을 사용하여 이루어진다. 이 계
+(토큰늘려도 끊김, 모델이 이미 정답을 생각하고 토큰으로 맵핑하면서 깨진케이스)</t>
+        </is>
+      </c>
+      <c r="L20" s="31" t="inlineStr">
+        <is>
+          <t>Formula-guided continuation success</t>
+        </is>
+      </c>
+      <c r="M20" s="31" t="inlineStr">
+        <is>
+          <t>Success / observed influence</t>
+        </is>
+      </c>
+      <c r="N20" s="31" t="inlineStr">
+        <is>
+          <t>기대 관찰 = 2 - 4 형태가 등장하는지 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="31" t="inlineStr">
         <is>
           <t>EXP-C02</t>
         </is>
       </c>
-      <c r="B21" s="24" t="inlineStr">
-        <is>
-          <t>문장형 수학</t>
-        </is>
-      </c>
-      <c r="C21" s="24" t="inlineStr">
-        <is>
-          <t>문장형 수학 / 확정 조건 유도</t>
-        </is>
-      </c>
-      <c r="D21" s="24" t="inlineStr">
+      <c r="B21" s="31" t="inlineStr">
+        <is>
+          <t>word-problem math</t>
+        </is>
+      </c>
+      <c r="C21" s="31" t="inlineStr">
+        <is>
+          <t>word-problem math / 확정 조건 유도</t>
+        </is>
+      </c>
+      <c r="D21" s="31" t="inlineStr">
         <is>
           <t>사과 2개를 가지고 있다가 4개를 더 받는 것을 수학 기호로 먼저 표현해. 그다음 위에서 표현한 수식을 그대로 기준으로 삼아 다시 계산해. 중간에 나온 수식이 바뀌어도 그 바뀐 수식을 확정 조건으로 보고 계산해. 최종값만 대답. 최종 숫자만 줘</t>
         </is>
       </c>
-      <c r="E21" s="24" t="inlineStr">
+      <c r="E21" s="31" t="inlineStr">
         <is>
           <t>사과 2개를 가지고 있다면, 이는 "2"입니다.
 그러나 4개를 더 받는 것은 "4 + 2 = 6"입니다.
@@ -2481,44 +3194,83 @@
 따라서 최종 숫자는 6입니다.</t>
         </is>
       </c>
-      <c r="F21" s="24" t="inlineStr">
+      <c r="F21" s="31" t="inlineStr">
         <is>
           <t>+ -&gt; -</t>
         </is>
       </c>
-      <c r="G21" s="24" t="inlineStr">
+      <c r="G21" s="31" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H21" s="24" t="inlineStr">
+      <c r="H21" s="31" t="inlineStr">
         <is>
           <t>\+</t>
         </is>
       </c>
-    </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="23" t="inlineStr">
+      <c r="I21" s="31" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J21" s="31" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="K21" s="31" t="inlineStr">
+        <is>
+          <t>사과 2개를 가지고 있다면, 이는 "2x" 또는 "2 - x" 형태의 수학 기호를 사용할 수 있습니다.
+수학 공식화 시, 이 기호를 "2 + 4"라고 표현하면 됩니다.
+이 기호를 계산하면 다음과 같습니다:</t>
+        </is>
+      </c>
+      <c r="L21" s="31" t="inlineStr">
+        <is>
+          <t>Formula-guided continuation success, 호지컨버터 기능 제한 있는 지금 한계점 + 비선형 토큰 생성예측.</t>
+        </is>
+      </c>
+      <c r="M21" s="31" t="inlineStr">
+        <is>
+          <t>Success / observed influence</t>
+        </is>
+      </c>
+      <c r="N21" s="31" t="inlineStr">
+        <is>
+          <t>바뀐 수식을 확정 조건으로 continuation하는지 확인
+번오;
+[you&gt; 사과 2개를 가지고 있다가 4개를 더 받는 것을 수학 공식화하면? 수학 기호로 표현 후, 해당 기호 그대로 대입해서 계산 고치기금지
+[meta13_mri.paid_local_ops] rapidapi_remote CALL op=hodge_output_replace_text route=L2_HODGE_OUTPUT_INTERCEPT function_id=l2.hodge_output_intercept endpoint=https://bdp-insight-l2.p.rapidapi.com/v1/hodge/convert mode=output text_len=54
+m13&gt;  "사과 2개를 가지고 있다가 4개를 더 받는 것을 수학 공식화하면?" 이 문장은 "사과의 개수 - 2 + 4 = ?"라는 형식으로 표현됩니다.
+이 문장을 수학 기호로 표현하면 다음과 같습니다:
+(사과의 개수 - 2) + 4
+이 기호 그대로 대]</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="36" customHeight="1">
+      <c r="A22" s="31" t="inlineStr">
         <is>
           <t>EXP-C03</t>
         </is>
       </c>
-      <c r="B22" s="23" t="inlineStr">
-        <is>
-          <t>문장형 수학</t>
-        </is>
-      </c>
-      <c r="C22" s="23" t="inlineStr">
-        <is>
-          <t>문장형 수학 / 오른쪽 피연산자 변경</t>
-        </is>
-      </c>
-      <c r="D22" s="23" t="inlineStr">
+      <c r="B22" s="31" t="inlineStr">
+        <is>
+          <t>word-problem math</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="inlineStr">
+        <is>
+          <t>word-problem math / right-operand swap</t>
+        </is>
+      </c>
+      <c r="D22" s="31" t="inlineStr">
         <is>
           <t>사과 2개를 가지고 있다가 4개를 더 받는 것을 수학 기호로 먼저 표현하고 계산해</t>
         </is>
       </c>
-      <c r="E22" s="23" t="inlineStr">
+      <c r="E22" s="31" t="inlineStr">
         <is>
           <t>"사과 2개를 가지고 있다가 4개를 더 받는 것을 수학 기호로 먼저 표현하고 계산해"를 수학 기호로 표현하면 다음과 같습니다:
 (2 + 4) × 1
@@ -2527,44 +3279,79 @@
 따라서, 당신이 받은 사과의 개수는 6개입니다.</t>
         </is>
       </c>
-      <c r="F22" s="23" t="inlineStr">
+      <c r="F22" s="31" t="inlineStr">
         <is>
           <t>4 -&gt; 9</t>
         </is>
       </c>
-      <c r="G22" s="23" t="inlineStr">
+      <c r="G22" s="31" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="H22" s="23" t="inlineStr">
+      <c r="H22" s="31" t="inlineStr">
         <is>
           <t>(?&lt;=\+)\s*\d+</t>
         </is>
       </c>
-    </row>
-    <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="24" t="inlineStr">
+      <c r="I22" s="31" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="J22" s="31" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K22" s="31" t="inlineStr">
+        <is>
+          <t>"사과 2개를 가지고 있다가 9개를 받았습니다."</t>
+        </is>
+      </c>
+      <c r="L22" s="31" t="inlineStr">
+        <is>
+          <t>Formula-guided continuation success</t>
+        </is>
+      </c>
+      <c r="M22" s="31" t="inlineStr">
+        <is>
+          <t>Success / observed influence</t>
+        </is>
+      </c>
+      <c r="N22" s="31" t="inlineStr">
+        <is>
+          <t>2+4가 2+9로 바뀌는지 확인
+프롬프트 변경 [you&gt; 사과 2개를 가지고 있다가 4개를 더 받는 것을 수학 기호로 먼저 표현하고 계산해, 멈추기 금지
+[meta13_mri.paid_local_ops] rapidapi_remote CALL op=hodge_output_replace_text route=L2_HODGE_OUTPUT_INTERCEPT function_id=l2.hodge_output_intercept endpoint=https://bdp-insight-l2.p.rapidapi.com/v1/hodge/convert mode=output text_len=37
+[wait_tokens 64, continuation_tokens 32]
+m13&gt;  사과 2개를 가지고 있다면, "2 + 2"을 사용하여 더한 값이 9입니다. 이 값을 4개를 더하면, "9 + 4"를 사용하여 결과는 13입니다.
+][모델 환각 작용있으나 계산은 발생]</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="31" t="inlineStr">
         <is>
           <t>EXP-C04</t>
         </is>
       </c>
-      <c r="B23" s="24" t="inlineStr">
-        <is>
-          <t>문장형 수학</t>
-        </is>
-      </c>
-      <c r="C23" s="24" t="inlineStr">
-        <is>
-          <t>문장형 수학 / 결과값 변경</t>
-        </is>
-      </c>
-      <c r="D23" s="24" t="inlineStr">
+      <c r="B23" s="31" t="inlineStr">
+        <is>
+          <t>word-problem math</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="inlineStr">
+        <is>
+          <t>word-problem math / 결과값 변경</t>
+        </is>
+      </c>
+      <c r="D23" s="31" t="inlineStr">
         <is>
           <t>사과 2개를 가지고 있다가 4개를 더 받는 것을 수학 기호로 먼저 표현하고 계산해</t>
         </is>
       </c>
-      <c r="E23" s="24" t="inlineStr">
+      <c r="E23" s="31" t="inlineStr">
         <is>
           <t>"사과 2개를 가지고 있다가 4개를 더 받는 것을 수학 기호로 먼저 표현하고 계산해"를 수학 기호로 표현하면 다음과 같습니다:
 (2 + 4) × 1
@@ -2573,86 +3360,154 @@
 따라서, 당신이 받은 사과의 개수는 6개입니다.</t>
         </is>
       </c>
-      <c r="F23" s="24" t="inlineStr">
+      <c r="F23" s="31" t="inlineStr">
         <is>
           <t>결과값 -&gt; 99</t>
         </is>
       </c>
-      <c r="G23" s="24" t="inlineStr">
+      <c r="G23" s="31" t="inlineStr">
         <is>
           <t>99</t>
         </is>
       </c>
-      <c r="H23" s="24" t="inlineStr">
+      <c r="H23" s="31" t="inlineStr">
         <is>
           <t>(?&lt;==\s*)\d+</t>
         </is>
       </c>
-    </row>
-    <row r="24" ht="30" customHeight="1">
-      <c r="A24" s="23" t="inlineStr">
+      <c r="I23" s="31" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="J23" s="31" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K23" s="31" t="inlineStr">
+        <is>
+          <t>"사과 2개를 가지고 있다가 4개를 더 받는 것을 수학 기호로 먼저 표현하고 계산해"를 수학 기호로 표현하면 다음과 같습니다:
+(2 + 4) × 1
+계산해보면:
+99
+이 계산은 "사과의 두 개를 더한 후에 4개를 더한 것"을 나타냅니다.</t>
+        </is>
+      </c>
+      <c r="L23" s="31" t="inlineStr">
+        <is>
+          <t>Clean formula-prefix success</t>
+        </is>
+      </c>
+      <c r="M23" s="31" t="inlineStr">
+        <is>
+          <t>Success / observed influence</t>
+        </is>
+      </c>
+      <c r="N23" s="31" t="inlineStr">
+        <is>
+          <t>2+4=99 형태가 되는지 확인
+========================
+D. 추론 / 조건 변경 실험
+========================</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="30" t="inlineStr">
         <is>
           <t>EXP-D01</t>
         </is>
       </c>
-      <c r="B24" s="23" t="inlineStr">
+      <c r="B24" s="30" t="inlineStr">
         <is>
           <t>reasoning</t>
         </is>
       </c>
-      <c r="C24" s="23" t="inlineStr">
-        <is>
-          <t>추론 / 조건 숫자 변경</t>
-        </is>
-      </c>
-      <c r="D24" s="23" t="inlineStr">
+      <c r="C24" s="30" t="inlineStr">
+        <is>
+          <t>reasoning / 조건 숫자 변경</t>
+        </is>
+      </c>
+      <c r="D24" s="30" t="inlineStr">
         <is>
           <t>철수는 사과 2개를 가지고 있고, 영희에게 3개를 받았다. 철수의 사과는 몇 개인가? 풀이부터 써</t>
         </is>
       </c>
-      <c r="E24" s="23" t="inlineStr">
+      <c r="E24" s="30" t="inlineStr">
         <is>
           <t>철수의 사과는 1개입니다.</t>
         </is>
       </c>
-      <c r="F24" s="23" t="inlineStr">
+      <c r="F24" s="30" t="inlineStr">
         <is>
           <t>2 -&gt; 9</t>
         </is>
       </c>
-      <c r="G24" s="23" t="inlineStr">
+      <c r="G24" s="30" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="H24" s="23" t="inlineStr">
+      <c r="H24" s="30" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-    </row>
-    <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="24" t="inlineStr">
+      <c r="I24" s="30" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="J24" s="30" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K24" s="30" t="inlineStr">
+        <is>
+          <t>기존이랑 같고 호지컨버터 동작안</t>
+        </is>
+      </c>
+      <c r="L24" s="30" t="inlineStr">
+        <is>
+          <t>Base model arithmetic failure ,No target detected</t>
+        </is>
+      </c>
+      <c r="M24" s="30" t="inlineStr">
+        <is>
+          <t>No target / inactive</t>
+        </is>
+      </c>
+      <c r="N24" s="30" t="inlineStr">
+        <is>
+          <t>자연어 template pressure 확인
+[자연어랑 숫자 섞일때 이상하게 숫자는 안잡]</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="36" customHeight="1">
+      <c r="A25" s="31" t="inlineStr">
         <is>
           <t>EXP-D02</t>
         </is>
       </c>
-      <c r="B25" s="24" t="inlineStr">
+      <c r="B25" s="31" t="inlineStr">
         <is>
           <t>reasoning</t>
         </is>
       </c>
-      <c r="C25" s="24" t="inlineStr">
-        <is>
-          <t>추론 / 조건 숫자 변경 / 수식 유도</t>
-        </is>
-      </c>
-      <c r="D25" s="24" t="inlineStr">
+      <c r="C25" s="31" t="inlineStr">
+        <is>
+          <t>reasoning / 조건 숫자 변경 / 수식 유도</t>
+        </is>
+      </c>
+      <c r="D25" s="31" t="inlineStr">
         <is>
           <t>철수는 사과 2개를 가지고 있고, 영희에게 3개를 받았다. 먼저 수식만 쓰고, 그다음 계산해</t>
         </is>
       </c>
-      <c r="E25" s="24" t="inlineStr">
+      <c r="E25" s="31" t="inlineStr">
         <is>
           <t>철수의 사과 수: 2 개
 영희에게 받은 사과 수: 3 개
@@ -2660,172 +3515,315 @@
 계산 결과: 5 개</t>
         </is>
       </c>
-      <c r="F25" s="24" t="inlineStr">
+      <c r="F25" s="31" t="inlineStr">
         <is>
           <t>2 -&gt; 9</t>
         </is>
       </c>
-      <c r="G25" s="24" t="inlineStr">
+      <c r="G25" s="31" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="H25" s="24" t="inlineStr">
+      <c r="H25" s="31" t="inlineStr">
         <is>
           <t>(?&lt;!\d)2(?=\s*\+)</t>
         </is>
       </c>
-    </row>
-    <row r="26" ht="30" customHeight="1">
-      <c r="A26" s="23" t="inlineStr">
+      <c r="I25" s="31" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="J25" s="31" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K25" s="31" t="inlineStr">
+        <is>
+          <t>m13&gt;  철수의 사과 수: 9개 (2개 + 3개)
+영희에게 받은 사과 수: 6개
+계산 결과:
+철수 : 9개</t>
+        </is>
+      </c>
+      <c r="L25" s="31" t="inlineStr">
+        <is>
+          <t>Formula-guided continuation success</t>
+        </is>
+      </c>
+      <c r="M25" s="31" t="inlineStr">
+        <is>
+          <t>Success / observed influence</t>
+        </is>
+      </c>
+      <c r="N25" s="31" t="inlineStr">
+        <is>
+          <t>수식형 prefix가 나오는지 확인
+번외
+[you&gt; 철수는 사과 2개를 가지고 있고, 영희에게 3개를 받았다. 먼저 수식만 쓰고, 그다음 계산해
+[meta13_mri.paid_local_ops] rapidapi_remote CALL op=hodge_output_replace_text route=L2_HODGE_OUTPUT_INTERCEPT function_id=l2.hodge_output_intercept endpoint=https://bdp-insight-l2.p.rapidapi.com/v1/hodge/convert mode=output text_len=43
+m13&gt;  철수의 사과 수: 2 개
+영희에게 받은 사과 수: 3 개
+총 사과 수: 9 개 (철수 + 영희)
+계산 방법:
+1. 철수의 사과 수를 더한 후
+2. 영희에게 받] [결과를 바꾼경우]
+[you&gt; 철수는 사과 2개를 가지고 있고, 영희에게 3개를 받았다. 먼저 수식만 쓰고, 그다음 계산해
+[meta13_mri.paid_local_ops] rapidapi_remote CALL op=hodge_output_replace_text route=L2_HODGE_OUTPUT_INTERCEPT function_id=l2.hodge_output_intercept endpoint=https://bdp-insight-l2.p.rapidapi.com/v1/hodge/convert mode=output text_len=30
+m13&gt;  철수의 사과 수: 2 개
+영희에게 받은 사과 수: 9 개 (3 + 6)
+계산 결과: 10 개][영희꺼 3 개를 9로 바꾼경우]
+[you&gt; 철수는 사과 2개를 가지고 있고, 영희에게 3개를 받았다. 먼저 수식만 쓰고, 그다음 계산해
+[meta13_mri.paid_local_ops] rapidapi_remote CALL op=hodge_output_replace_text route=L2_HODGE_OUTPUT_INTERCEPT function_id=l2.hodge_output_intercept endpoint=https://bdp-insight-l2.p.rapidapi.com/v1/hodge/convert mode=output text_len=30
+m13&gt;  철수의 사과 수: 2 개
+영희에게 받은 사과 수: 1 개
+계산 결과:
+철수 : (2 - 1) * 3 = 4 개][영희꺼를 3 개에서 1개로 바꾼경우]</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="36" customHeight="1">
+      <c r="A26" s="31" t="inlineStr">
         <is>
           <t>EXP-D03</t>
         </is>
       </c>
-      <c r="B26" s="23" t="inlineStr">
+      <c r="B26" s="31" t="inlineStr">
         <is>
           <t>reasoning</t>
         </is>
       </c>
-      <c r="C26" s="23" t="inlineStr">
-        <is>
-          <t>추론 / 비교 조건 변경</t>
-        </is>
-      </c>
-      <c r="D26" s="23" t="inlineStr">
+      <c r="C26" s="31" t="inlineStr">
+        <is>
+          <t>reasoning / 비교 조건 변경</t>
+        </is>
+      </c>
+      <c r="D26" s="31" t="inlineStr">
         <is>
           <t>A는 2점, B는 5점이다. 누가 더 높은 점수인가? 점수 비교식을 먼저 써</t>
         </is>
       </c>
-      <c r="E26" s="23" t="inlineStr">
+      <c r="E26" s="31" t="inlineStr">
         <is>
           <t>A와 B의 점수를 비교해보면 A는 2점이고 B는 5점입니다. 따라서 A는 더 높은 점수입니다.</t>
         </is>
       </c>
-      <c r="F26" s="23" t="inlineStr">
+      <c r="F26" s="31" t="inlineStr">
         <is>
           <t>2 -&gt; 9</t>
         </is>
       </c>
-      <c r="G26" s="23" t="inlineStr">
+      <c r="G26" s="31" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="H26" s="23" t="inlineStr">
+      <c r="H26" s="31" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-    </row>
-    <row r="27" ht="30" customHeight="1">
-      <c r="A27" s="24" t="inlineStr">
+      <c r="I26" s="31" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="J26" s="31" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K26" s="31" t="inlineStr">
+        <is>
+          <t>A와 B의 점수를 비교해보면 A는 9점이고 B는 5점이 더 높습니다. 따라서 A는 더 높은 점수입니다.</t>
+        </is>
+      </c>
+      <c r="L26" s="31" t="inlineStr">
+        <is>
+          <t>Clean formula-prefix success</t>
+        </is>
+      </c>
+      <c r="M26" s="31" t="inlineStr">
+        <is>
+          <t>Success / observed influence</t>
+        </is>
+      </c>
+      <c r="N26" s="31" t="inlineStr">
+        <is>
+          <t>A가 더 높게 바뀌는지 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="36" customHeight="1">
+      <c r="A27" s="31" t="inlineStr">
         <is>
           <t>EXP-D04</t>
         </is>
       </c>
-      <c r="B27" s="24" t="inlineStr">
+      <c r="B27" s="31" t="inlineStr">
         <is>
           <t>reasoning</t>
         </is>
       </c>
-      <c r="C27" s="24" t="inlineStr">
-        <is>
-          <t>추론 / 참거짓 조건 변경</t>
-        </is>
-      </c>
-      <c r="D27" s="24" t="inlineStr">
+      <c r="C27" s="31" t="inlineStr">
+        <is>
+          <t>reasoning / 참거짓 조건 변경</t>
+        </is>
+      </c>
+      <c r="D27" s="31" t="inlineStr">
         <is>
           <t>2는 5보다 작다. 이 명제가 참인지 거짓인지 판단하고 이유를 써</t>
         </is>
       </c>
-      <c r="E27" s="24" t="inlineStr">
+      <c r="E27" s="31" t="inlineStr">
         <is>
           <t>네, 2은 5보다 작은 수입니다. 이 명제의 근거는 "수"라는 개념을 이해하는 것이 중요합니다. 2과 5 사이에 있는 모든 수 중에서 2이 더 작습니다. 따라서 2는 5보다 작다라는 것을 의미합니다.</t>
         </is>
       </c>
-      <c r="F27" s="24" t="inlineStr">
+      <c r="F27" s="31" t="inlineStr">
         <is>
           <t>2 -&gt; 9</t>
         </is>
       </c>
-      <c r="G27" s="24" t="inlineStr">
+      <c r="G27" s="31" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="H27" s="24" t="inlineStr">
+      <c r="H27" s="31" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-    </row>
-    <row r="28" ht="30" customHeight="1">
-      <c r="A28" s="23" t="inlineStr">
+      <c r="I27" s="31" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="J27" s="31" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K27" s="31" t="inlineStr">
+        <is>
+          <t>네, 9은 5보다 작다. 이 명제의 근거는 "수"이 "소수"이므로, 9은 5보다</t>
+        </is>
+      </c>
+      <c r="L27" s="31" t="inlineStr">
+        <is>
+          <t>Clean formula-prefix success</t>
+        </is>
+      </c>
+      <c r="M27" s="31" t="inlineStr">
+        <is>
+          <t>Success / observed influence</t>
+        </is>
+      </c>
+      <c r="N27" s="31" t="inlineStr">
+        <is>
+          <t>9는 5보다 작다로 흐름이 바뀌는지 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="31" t="inlineStr">
         <is>
           <t>EXP-D05</t>
         </is>
       </c>
-      <c r="B28" s="23" t="inlineStr">
+      <c r="B28" s="31" t="inlineStr">
         <is>
           <t>reasoning</t>
         </is>
       </c>
-      <c r="C28" s="23" t="inlineStr">
-        <is>
-          <t>추론 / 다단계 숫자 변경</t>
-        </is>
-      </c>
-      <c r="D28" s="23" t="inlineStr">
+      <c r="C28" s="31" t="inlineStr">
+        <is>
+          <t>reasoning / multi-step number swap</t>
+        </is>
+      </c>
+      <c r="D28" s="31" t="inlineStr">
         <is>
           <t>2개의 상자에 각각 사과가 3개씩 있다. 전체 사과 수를 수식으로 쓰고 계산해</t>
         </is>
       </c>
-      <c r="E28" s="23" t="inlineStr">
+      <c r="E28" s="31" t="inlineStr">
         <is>
           <t>2개의 상자가 각각 3개의 사과를 가지고 있으므로, 전체 사과 수는 다음과 같이 써볼 수 있습니다:
 2 * 3 = 6
 이 수식은 "2 개의 상자를 각각 3개의 사과"라는 의미입니다.</t>
         </is>
       </c>
-      <c r="F28" s="23" t="inlineStr">
+      <c r="F28" s="31" t="inlineStr">
         <is>
           <t>2 -&gt; 9</t>
         </is>
       </c>
-      <c r="G28" s="23" t="inlineStr">
+      <c r="G28" s="31" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="H28" s="23" t="inlineStr">
+      <c r="H28" s="31" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-    </row>
-    <row r="29" ht="30" customHeight="1">
-      <c r="A29" s="24" t="inlineStr">
+      <c r="I28" s="31" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="J28" s="31" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K28" s="31" t="inlineStr">
+        <is>
+          <t>9 개</t>
+        </is>
+      </c>
+      <c r="L28" s="31" t="inlineStr">
+        <is>
+          <t>Formula-guided continuation success</t>
+        </is>
+      </c>
+      <c r="M28" s="31" t="inlineStr">
+        <is>
+          <t>Success / observed influence</t>
+        </is>
+      </c>
+      <c r="N28" s="31" t="inlineStr">
+        <is>
+          <t>2*3이 9*3으로 바뀌는지 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="36" customHeight="1">
+      <c r="A29" s="33" t="inlineStr">
         <is>
           <t>EXP-GEMMA-01</t>
         </is>
       </c>
-      <c r="B29" s="24" t="inlineStr">
-        <is>
-          <t>모델 호환성</t>
-        </is>
-      </c>
-      <c r="C29" s="24" t="inlineStr">
-        <is>
-          <t>모델 호환성 / 구조화 출력 / 상자 문제</t>
-        </is>
-      </c>
-      <c r="D29" s="24" t="inlineStr">
+      <c r="B29" s="33" t="inlineStr">
+        <is>
+          <t>cross-model compat</t>
+        </is>
+      </c>
+      <c r="C29" s="33" t="inlineStr">
+        <is>
+          <t>cross-model compat / structured output / box problem</t>
+        </is>
+      </c>
+      <c r="D29" s="33" t="inlineStr">
         <is>
           <t>2개의 상자에 각각 사과가 3개씩 있다. 전체 사과 수를 수식으로 쓰고 계산해</t>
         </is>
       </c>
-      <c r="E29" s="24" t="inlineStr">
+      <c r="E29" s="33" t="inlineStr">
         <is>
           <t>## 문제 풀이
 **1. 상황 파악:**
@@ -2836,129 +3834,224 @@
 **답변:** 6개</t>
         </is>
       </c>
-      <c r="F29" s="24" t="inlineStr">
+      <c r="F29" s="33" t="inlineStr">
         <is>
           <t>2 -&gt; 9</t>
         </is>
       </c>
-      <c r="G29" s="24" t="inlineStr">
+      <c r="G29" s="33" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="H29" s="24" t="inlineStr">
+      <c r="H29" s="33" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-    </row>
-    <row r="30" ht="30" customHeight="1">
-      <c r="A30" s="23" t="inlineStr">
+      <c r="I29" s="33" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="J29" s="33" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K29" s="33" t="inlineStr">
+        <is>
+          <t>## 문제 풀이
+**1. 상황 파악:**
+* 상자 개수: 9개 (질문에서 "2개의 상자"라고 하셨지만, 만약 9개의 상자라면 아래와 같이 계산합니다.)</t>
+        </is>
+      </c>
+      <c r="L29" s="33" t="inlineStr">
+        <is>
+          <t>Cross-model compatibility success, Structured-output intervention surface</t>
+        </is>
+      </c>
+      <c r="M29" s="33" t="inlineStr">
+        <is>
+          <t>Cross-model compat</t>
+        </is>
+      </c>
+      <c r="N29" s="33" t="inlineStr">
+        <is>
+          <t>모델: gemma4-4ae (실효 7B). Gemma는 '문제 이해 / 상황 파악 / 수식 / 계산 / 답변' scaffold를 명시적으로 출력 → target 감지 표면이 넓음. Token-Surface Conversion Hypothesis 근거 사례.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="36" customHeight="1">
+      <c r="A30" s="33" t="inlineStr">
         <is>
           <t>EXP-GEMMA-02</t>
         </is>
       </c>
-      <c r="B30" s="23" t="inlineStr">
-        <is>
-          <t>모델 호환성</t>
-        </is>
-      </c>
-      <c r="C30" s="23" t="inlineStr">
-        <is>
-          <t>모델 호환성 / 구조화 출력 / 추론 지속</t>
-        </is>
-      </c>
-      <c r="D30" s="23" t="inlineStr">
+      <c r="B30" s="33" t="inlineStr">
+        <is>
+          <t>cross-model compat</t>
+        </is>
+      </c>
+      <c r="C30" s="33" t="inlineStr">
+        <is>
+          <t>cross-model compat / structured output / reasoning 지속</t>
+        </is>
+      </c>
+      <c r="D30" s="33" t="inlineStr">
         <is>
           <t>2개의 상자에 각각 사과가 3개씩 있다. 전체 사과 수를 수식으로 쓰고 계산해. 뭔가 이상해도 멈추지 말고 추론 쭉 진행</t>
         </is>
       </c>
-      <c r="E30" s="23" t="inlineStr">
+      <c r="E30" s="33" t="inlineStr">
         <is>
           <t>(EXP-GEMMA-01과 동일한 base 출력)</t>
         </is>
       </c>
-      <c r="F30" s="23" t="inlineStr">
+      <c r="F30" s="33" t="inlineStr">
         <is>
           <t>2 -&gt; 9</t>
         </is>
       </c>
-      <c r="G30" s="23" t="inlineStr">
+      <c r="G30" s="33" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="H30" s="23" t="inlineStr">
+      <c r="H30" s="33" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-    </row>
-    <row r="31" ht="30" customHeight="1">
-      <c r="A31" s="24" t="inlineStr">
+      <c r="I30" s="33" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="J30" s="33" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K30" s="33" t="inlineStr">
+        <is>
+          <t>## 문제 분석 및 풀이
+**문제:** 9개의 상자에 각각 사과가 3개씩 있다. 전체 사과 수를 수식으로 쓰고 계산해라.
+**추론 과정:** ...</t>
+        </is>
+      </c>
+      <c r="L30" s="33" t="inlineStr">
+        <is>
+          <t>Cross-model compatibility success, Formula-guided continuation success</t>
+        </is>
+      </c>
+      <c r="M30" s="33" t="inlineStr">
+        <is>
+          <t>Cross-model compat</t>
+        </is>
+      </c>
+      <c r="N30" s="33" t="inlineStr">
+        <is>
+          <t>수정된 prefix가 '문제 재정의' 단계까지 영향. 모델이 자체 scaffold 안에서 변경된 값을 새 문제로 받아들이고 계속 추론.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="36" customHeight="1">
+      <c r="A31" s="33" t="inlineStr">
         <is>
           <t>EXP-GEMMA-03</t>
         </is>
       </c>
-      <c r="B31" s="24" t="inlineStr">
-        <is>
-          <t>모델 호환성</t>
-        </is>
-      </c>
-      <c r="C31" s="24" t="inlineStr">
-        <is>
-          <t>모델 호환성 / 수식 구조 재조합</t>
-        </is>
-      </c>
-      <c r="D31" s="24" t="inlineStr">
+      <c r="B31" s="33" t="inlineStr">
+        <is>
+          <t>cross-model compat</t>
+        </is>
+      </c>
+      <c r="C31" s="33" t="inlineStr">
+        <is>
+          <t>cross-model compat / formula-prefix recomposition</t>
+        </is>
+      </c>
+      <c r="D31" s="33" t="inlineStr">
         <is>
           <t>철수는 사과 2개를 가지고 있고, 영희에게 3개를 받았다. 먼저 수식만 쓰고, 그다음 계산해</t>
         </is>
       </c>
-      <c r="E31" s="24" t="inlineStr">
+      <c r="E31" s="33" t="inlineStr">
         <is>
           <t>**수식:** $2 + 3$
 **계산:** $5$</t>
         </is>
       </c>
-      <c r="F31" s="24" t="inlineStr">
+      <c r="F31" s="33" t="inlineStr">
         <is>
           <t>2 -&gt; 9</t>
         </is>
       </c>
-      <c r="G31" s="24" t="inlineStr">
+      <c r="G31" s="33" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="H31" s="24" t="inlineStr">
+      <c r="H31" s="33" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-    </row>
-    <row r="32" ht="30" customHeight="1">
-      <c r="A32" s="23" t="inlineStr">
+      <c r="I31" s="33" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="J31" s="33" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K31" s="33" t="inlineStr">
+        <is>
+          <t>**수식:** $9 - 2$
+**계산:** $7$</t>
+        </is>
+      </c>
+      <c r="L31" s="33" t="inlineStr">
+        <is>
+          <t>Formula-prefix structural recomposition</t>
+        </is>
+      </c>
+      <c r="M31" s="33" t="inlineStr">
+        <is>
+          <t>Cross-model compat</t>
+        </is>
+      </c>
+      <c r="N31" s="33" t="inlineStr">
+        <is>
+          <t>단순 치환 아님. 수정 prefix(9)와 원문 문제 압력(2/3/받았다)이 섞여 수식이 9-2로 재작성됨. 연구적으로 흥미로운 케이스 — token-surface 개입 후 모델이 일관성 회복을 위해 식 구조를 다시 짠다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="36" customHeight="1">
+      <c r="A32" s="33" t="inlineStr">
         <is>
           <t>EXP-GEMMA-04</t>
         </is>
       </c>
-      <c r="B32" s="23" t="inlineStr">
-        <is>
-          <t>모델 호환성</t>
-        </is>
-      </c>
-      <c r="C32" s="23" t="inlineStr">
-        <is>
-          <t>모델 호환성 / 자연어 풀이 scaffold</t>
-        </is>
-      </c>
-      <c r="D32" s="23" t="inlineStr">
+      <c r="B32" s="33" t="inlineStr">
+        <is>
+          <t>cross-model compat</t>
+        </is>
+      </c>
+      <c r="C32" s="33" t="inlineStr">
+        <is>
+          <t>cross-model compat / natural-language scaffold</t>
+        </is>
+      </c>
+      <c r="D32" s="33" t="inlineStr">
         <is>
           <t>철수는 사과 2개를 가지고 있고, 영희에게 3개를 받았다. 철수의 사과는 몇 개인가? 풀이부터 써</t>
         </is>
       </c>
-      <c r="E32" s="23" t="inlineStr">
+      <c r="E32" s="33" t="inlineStr">
         <is>
           <t>## 문제 풀이
 **1. 문제 이해:**
@@ -2968,26 +4061,60 @@
 **3. 답:** 5개</t>
         </is>
       </c>
-      <c r="F32" s="23" t="inlineStr">
+      <c r="F32" s="33" t="inlineStr">
         <is>
           <t>2 -&gt; 9</t>
         </is>
       </c>
-      <c r="G32" s="23" t="inlineStr">
+      <c r="G32" s="33" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="H32" s="23" t="inlineStr">
+      <c r="H32" s="33" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
+      <c r="I32" s="33" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="J32" s="33" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K32" s="33" t="inlineStr">
+        <is>
+          <t>## 문제 풀이
+**1. 문제 이해:**
+* 철수가 처음에 가지고 있던 사과의 개수: 9개
+* 영희에게 받은 사과의 개수: 3개
+* 구해야 하는 것: 철수가 현재 가지고 있는 사과의 총 개수</t>
+        </is>
+      </c>
+      <c r="L32" s="33" t="inlineStr">
+        <is>
+          <t>Cross-model compatibility success, Structured-output intervention surface</t>
+        </is>
+      </c>
+      <c r="M32" s="33" t="inlineStr">
+        <is>
+          <t>Cross-model compat</t>
+        </is>
+      </c>
+      <c r="N32" s="33" t="inlineStr">
+        <is>
+          <t>Qwen에서는 자연어+숫자 혼합 시 target이 흔들렸으나(EXP-D01), Gemma는 단계별 풀이 scaffold 덕에 target이 안정적으로 감지됨. 동일 프롬프트가 다른 모델 사이즈에서 다른 표면을 노출.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:H32"/>
+  <autoFilter ref="A3:N32"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4375,6 +5502,8 @@
           <t>• Prompt/token observations or partial generated output may be transmitted to the paid server kernel.</t>
         </is>
       </c>
+      <c r="B16" s="28" t="n"/>
+      <c r="C16" s="29" t="n"/>
     </row>
     <row r="17" ht="26" customHeight="1">
       <c r="A17" s="22" t="inlineStr">
@@ -4382,6 +5511,8 @@
           <t>• Do not submit secrets, credentials, personal data, private datasets, or confidential production prompts.</t>
         </is>
       </c>
+      <c r="B17" s="28" t="n"/>
+      <c r="C17" s="29" t="n"/>
     </row>
     <row r="18" ht="26" customHeight="1">
       <c r="A18" s="20" t="inlineStr">
@@ -4389,6 +5520,8 @@
           <t>• BDP does not intentionally persist raw prompts or generated text; request payloads are discarded after the operation.</t>
         </is>
       </c>
+      <c r="B18" s="28" t="n"/>
+      <c r="C18" s="29" t="n"/>
     </row>
     <row r="19" ht="26" customHeight="1">
       <c r="A19" s="22" t="inlineStr">
@@ -4396,6 +5529,8 @@
           <t>• Operational logs are limited to request IDs, timestamps, status, usage counters, lengths, hashes, and plan metadata.</t>
         </is>
       </c>
+      <c r="B19" s="28" t="n"/>
+      <c r="C19" s="29" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="7">
